--- a/Assets/LingBoCanteen/1_Datatables/Excel/Ingredient.xlsx
+++ b/Assets/LingBoCanteen/1_Datatables/Excel/Ingredient.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="162">
   <si>
     <t>#</t>
   </si>
@@ -431,6 +431,9 @@
     <t>Flour</t>
   </si>
   <si>
+    <t>Flour_Output</t>
+  </si>
+  <si>
     <t>面团</t>
   </si>
   <si>
@@ -438,6 +441,9 @@
   </si>
   <si>
     <t>Egg</t>
+  </si>
+  <si>
+    <t>Egg_Output</t>
   </si>
   <si>
     <t>鸡蛋液</t>
@@ -1120,11 +1126,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1454,486 +1457,486 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85"/>
   <cols>
     <col min="2" max="2" width="13.1327433628319" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="2"/>
-    <col min="4" max="4" width="20.3185840707965" style="2" customWidth="1"/>
+    <col min="3" max="3" width="9" style="1"/>
+    <col min="4" max="4" width="20.3185840707965" style="1" customWidth="1"/>
     <col min="6" max="6" width="13.5309734513274" customWidth="1"/>
-    <col min="7" max="7" width="19.070796460177" style="2" customWidth="1"/>
-    <col min="8" max="8" width="17.3274336283186" style="2" customWidth="1"/>
-    <col min="9" max="9" width="19.2035398230088" style="2" customWidth="1"/>
+    <col min="7" max="7" width="19.070796460177" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.3274336283186" style="1" customWidth="1"/>
+    <col min="9" max="9" width="19.2035398230088" style="1" customWidth="1"/>
     <col min="10" max="10" width="10.7964601769912" customWidth="1"/>
-    <col min="11" max="11" width="12.1327433628319" style="2" customWidth="1"/>
-    <col min="12" max="12" width="17.6017699115044" style="2" customWidth="1"/>
+    <col min="11" max="11" width="12.1327433628319" style="1" customWidth="1"/>
+    <col min="12" max="12" width="17.6017699115044" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="J1" s="2"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="L4" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1">
         <v>1001</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="2" t="b">
+      <c r="E5" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="F5" s="2" t="b">
+      <c r="F5" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5" s="1">
         <v>3001</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L5" s="2">
+      <c r="L5" s="1">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1">
         <v>1002</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="2" t="b">
+      <c r="E6" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="F6" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="F6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="1">
         <v>3002</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="K6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6" s="1">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1">
         <v>1003</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="2" t="b">
+      <c r="E7" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="F7" s="2" t="b">
+      <c r="F7" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J7" s="1">
         <v>3003</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="K7" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L7" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1">
         <v>1004</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="2" t="b">
+      <c r="E8" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="F8" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2" t="s">
+      <c r="F8" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8" s="1">
         <v>3004</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="K8" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="L8" s="2">
+      <c r="L8" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1">
         <v>1005</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E9" s="2" t="b">
+      <c r="E9" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="F9" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" s="2" t="s">
+      <c r="F9" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="I9" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J9" s="1">
         <v>3005</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="K9" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="L9" s="2">
+      <c r="L9" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1">
         <v>1006</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E10" s="2" t="b">
+      <c r="E10" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="F10" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="2" t="s">
+      <c r="F10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="I10" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J10" s="1">
         <v>3006</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="K10" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="L10" s="2">
+      <c r="L10" s="1">
         <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1">
         <v>1007</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E11" s="2" t="b">
+      <c r="E11" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="F11" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11" s="2" t="s">
+      <c r="F11" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="I11" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J11" s="1">
         <v>3007</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="K11" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="L11" s="2">
+      <c r="L11" s="1">
         <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1">
         <v>1008</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="2" t="b">
+      <c r="E12" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="F12" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12" s="2" t="s">
+      <c r="F12" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="I12" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="J12" s="2">
+      <c r="J12" s="1">
         <v>3008</v>
       </c>
-      <c r="K12" s="2" t="s">
+      <c r="K12" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="L12" s="2">
+      <c r="L12" s="1">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1">
         <v>1009</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E13" s="2" t="b">
+      <c r="E13" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="F13" s="2" t="b">
+      <c r="F13" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="I13" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J13" s="1">
         <v>3009</v>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="K13" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="L13" s="2">
+      <c r="L13" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1">
         <v>1010</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E14" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" s="2" t="s">
+      <c r="E14" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="J14" s="2">
+      <c r="J14" s="1">
         <v>3010</v>
       </c>
-      <c r="K14" s="2" t="s">
+      <c r="K14" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="L14" s="2">
+      <c r="L14" s="1">
         <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="B15" s="2">
+      <c r="B15" s="1">
         <v>1011</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="1" t="s">
         <v>80</v>
       </c>
       <c r="E15" t="b">
@@ -1942,27 +1945,27 @@
       <c r="F15" t="b">
         <v>0</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="I15" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="J15" s="2">
+      <c r="J15" s="1">
         <v>3011</v>
       </c>
-      <c r="K15" s="2" t="s">
+      <c r="K15" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="L15" s="2">
+      <c r="L15" s="1">
         <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="B16" s="2">
+      <c r="B16" s="1">
         <v>1012</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="1" t="s">
         <v>83</v>
       </c>
       <c r="E16" t="b">
@@ -1971,30 +1974,30 @@
       <c r="F16" t="b">
         <v>0</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G16" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="I16" s="2" t="s">
+      <c r="I16" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="J16" s="2">
+      <c r="J16" s="1">
         <v>3012</v>
       </c>
-      <c r="K16" s="2" t="s">
+      <c r="K16" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="L16" s="2">
+      <c r="L16" s="1">
         <v>7</v>
       </c>
     </row>
     <row r="17" spans="2:12">
-      <c r="B17" s="2">
+      <c r="B17" s="1">
         <v>1013</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="1" t="s">
         <v>88</v>
       </c>
       <c r="E17" t="b">
@@ -2003,27 +2006,27 @@
       <c r="F17" t="b">
         <v>0</v>
       </c>
-      <c r="I17" s="2" t="s">
+      <c r="I17" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="J17" s="2">
+      <c r="J17" s="1">
         <v>3013</v>
       </c>
-      <c r="K17" s="2" t="s">
+      <c r="K17" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="L17" s="2">
+      <c r="L17" s="1">
         <v>15</v>
       </c>
     </row>
     <row r="18" spans="2:12">
-      <c r="B18" s="2">
+      <c r="B18" s="1">
         <v>1014</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="1" t="s">
         <v>91</v>
       </c>
       <c r="E18" t="b">
@@ -2032,33 +2035,33 @@
       <c r="F18" t="b">
         <v>1</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="G18" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="H18" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="I18" s="2" t="s">
+      <c r="I18" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="J18" s="2">
+      <c r="J18" s="1">
         <v>3014</v>
       </c>
-      <c r="K18" s="2" t="s">
+      <c r="K18" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="L18" s="2">
+      <c r="L18" s="1">
         <v>10</v>
       </c>
     </row>
     <row r="19" spans="2:12">
-      <c r="B19" s="2">
+      <c r="B19" s="1">
         <v>1015</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="1" t="s">
         <v>97</v>
       </c>
       <c r="E19" t="b">
@@ -2067,30 +2070,30 @@
       <c r="F19" t="b">
         <v>0</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="I19" s="2" t="s">
+      <c r="I19" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="J19" s="2">
+      <c r="J19" s="1">
         <v>3015</v>
       </c>
-      <c r="K19" s="2" t="s">
+      <c r="K19" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="L19" s="2">
+      <c r="L19" s="1">
         <v>9</v>
       </c>
     </row>
     <row r="20" spans="2:12">
-      <c r="B20" s="2">
+      <c r="B20" s="1">
         <v>1016</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="1" t="s">
         <v>102</v>
       </c>
       <c r="E20" t="b">
@@ -2099,30 +2102,30 @@
       <c r="F20" t="b">
         <v>0</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="G20" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="I20" s="2" t="s">
+      <c r="I20" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="J20" s="2">
+      <c r="J20" s="1">
         <v>3016</v>
       </c>
-      <c r="K20" s="2" t="s">
+      <c r="K20" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="L20" s="2">
+      <c r="L20" s="1">
         <v>8</v>
       </c>
     </row>
     <row r="21" spans="2:12">
-      <c r="B21" s="2">
+      <c r="B21" s="1">
         <v>1017</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="1" t="s">
         <v>107</v>
       </c>
       <c r="E21" t="b">
@@ -2131,27 +2134,27 @@
       <c r="F21" t="b">
         <v>0</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="G21" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="I21" s="2" t="s">
+      <c r="I21" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="J21" s="2">
+      <c r="J21" s="1">
         <v>3017</v>
       </c>
-      <c r="K21" s="2" t="s">
+      <c r="K21" s="1" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="22" spans="2:12">
-      <c r="B22" s="2">
+      <c r="B22" s="1">
         <v>1018</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="1" t="s">
         <v>112</v>
       </c>
       <c r="E22" t="b">
@@ -2160,27 +2163,27 @@
       <c r="F22" t="b">
         <v>0</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="G22" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="I22" s="2" t="s">
+      <c r="I22" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="J22" s="2">
+      <c r="J22" s="1">
         <v>3018</v>
       </c>
-      <c r="K22" s="2" t="s">
+      <c r="K22" s="1" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="23" spans="2:12">
-      <c r="B23" s="2">
+      <c r="B23" s="1">
         <v>1019</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="1" t="s">
         <v>117</v>
       </c>
       <c r="E23" t="b">
@@ -2189,27 +2192,27 @@
       <c r="F23" t="b">
         <v>0</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="G23" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="I23" s="2" t="s">
+      <c r="I23" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="J23" s="2">
+      <c r="J23" s="1">
         <v>3019</v>
       </c>
-      <c r="K23" s="2" t="s">
+      <c r="K23" s="1" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="24" spans="2:12">
-      <c r="B24" s="2">
+      <c r="B24" s="1">
         <v>1020</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="1" t="s">
         <v>122</v>
       </c>
       <c r="E24" t="b">
@@ -2218,27 +2221,27 @@
       <c r="F24" t="b">
         <v>0</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G24" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="I24" s="2" t="s">
+      <c r="I24" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="J24" s="2">
+      <c r="J24" s="1">
         <v>3020</v>
       </c>
-      <c r="K24" s="2" t="s">
+      <c r="K24" s="1" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="25" spans="2:12">
-      <c r="B25" s="2">
+      <c r="B25" s="1">
         <v>1021</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="1" t="s">
         <v>127</v>
       </c>
       <c r="E25" t="b">
@@ -2247,30 +2250,30 @@
       <c r="F25" t="b">
         <v>1</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="G25" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="H25" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="I25" s="2" t="s">
+      <c r="I25" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="J25" s="2">
+      <c r="J25" s="1">
         <v>3021</v>
       </c>
-      <c r="K25" s="2" t="s">
+      <c r="K25" s="1" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="26" spans="2:12">
-      <c r="B26" s="2">
+      <c r="B26" s="1">
         <v>1022</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="1" t="s">
         <v>133</v>
       </c>
       <c r="E26" t="b">
@@ -2279,155 +2282,161 @@
       <c r="F26" t="b">
         <v>0</v>
       </c>
-      <c r="J26" s="2">
+      <c r="I26" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="J26" s="1">
         <v>3022</v>
       </c>
-      <c r="K26" s="2" t="s">
-        <v>134</v>
+      <c r="K26" s="1" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="27" spans="2:12">
-      <c r="B27" s="2">
+      <c r="B27" s="1">
         <v>1023</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D27" s="2" t="s">
+      <c r="C27" s="1" t="s">
         <v>136</v>
       </c>
+      <c r="D27" s="1" t="s">
+        <v>137</v>
+      </c>
       <c r="E27" t="b">
         <v>0</v>
       </c>
       <c r="F27" t="b">
         <v>0</v>
       </c>
-      <c r="J27" s="2">
+      <c r="I27" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J27" s="1">
         <v>3023</v>
       </c>
-      <c r="K27" s="2" t="s">
-        <v>137</v>
+      <c r="K27" s="1" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="28" spans="2:12">
       <c r="B28" s="1">
         <v>4001</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>139</v>
+      <c r="C28" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="29" spans="2:12">
       <c r="B29" s="1">
         <v>4002</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>141</v>
+      <c r="C29" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="30" spans="2:12">
       <c r="B30" s="1">
         <v>4003</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>143</v>
+      <c r="C30" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="31" spans="2:12">
       <c r="B31" s="1">
         <v>4004</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>145</v>
+      <c r="C31" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="32" spans="2:12">
       <c r="B32" s="1">
         <v>4005</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>147</v>
+      <c r="C32" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="1">
         <v>4006</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>149</v>
+      <c r="C33" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="1">
         <v>5001</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>151</v>
+      <c r="C34" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="1">
         <v>5002</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>153</v>
+      <c r="C35" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="1">
         <v>5003</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>155</v>
+      <c r="C36" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="1">
         <v>5004</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>157</v>
+      <c r="C37" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="1">
         <v>5005</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>159</v>
+      <c r="C38" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>161</v>
       </c>
     </row>
   </sheetData>
